--- a/data/trans_bre/P23_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 3,19</t>
+          <t>-8,89; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,15</t>
+          <t>-3,4; 9,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -1,19</t>
+          <t>-13,7; -1,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 6,28</t>
+          <t>-12,27; 6,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 9,42</t>
+          <t>-22,74; 9,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 34,37</t>
+          <t>-10,93; 33,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,22; -3,89</t>
+          <t>-37,31; -3,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 35,68</t>
+          <t>-42,69; 41,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -8,86</t>
+          <t>-19,78; -9,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 1,99</t>
+          <t>-9,25; 1,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,34; -0,21</t>
+          <t>-12,29; -0,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -4,78</t>
+          <t>-22,8; -4,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,61; -19,03</t>
+          <t>-38,16; -19,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 5,01</t>
+          <t>-19,52; 4,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,93; -0,16</t>
+          <t>-25,99; -1,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,02; -15,52</t>
+          <t>-62,08; -16,46</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -8,96</t>
+          <t>-20,58; -9,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -6,51</t>
+          <t>-17,38; -6,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -1,25</t>
+          <t>-11,92; -1,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,77</t>
+          <t>-8,04; 1,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,55; -18,6</t>
+          <t>-37,93; -19,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -14,89</t>
+          <t>-35,33; -14,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -3,48</t>
+          <t>-27,84; -2,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 7,13</t>
+          <t>-25,66; 7,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,19; -10,02</t>
+          <t>-22,18; -9,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 0,17</t>
+          <t>-12,16; -0,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -1,77</t>
+          <t>-12,92; -1,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 15,61</t>
+          <t>-7,63; 15,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,89; -24,44</t>
+          <t>-47,41; -23,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 0,41</t>
+          <t>-25,11; -0,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,31; -4,39</t>
+          <t>-28,46; -3,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 174,81</t>
+          <t>-25,75; 153,65</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,95; -15,45</t>
+          <t>-26,65; -15,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,2; -14,98</t>
+          <t>-26,59; -14,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -1,45</t>
+          <t>-13,22; -1,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -4,25</t>
+          <t>-13,36; -4,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-73,69; -51,34</t>
+          <t>-74,35; -51,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -46,1</t>
+          <t>-67,89; -45,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -4,9</t>
+          <t>-39,71; -6,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,05; -14,62</t>
+          <t>-39,38; -15,6</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -12,07</t>
+          <t>-21,18; -11,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -5,84</t>
+          <t>-16,54; -6,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -4,21</t>
+          <t>-14,69; -4,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -5,26</t>
+          <t>-17,59; -4,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-95,6; -78,05</t>
+          <t>-95,75; -77,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,78; -42,98</t>
+          <t>-82,89; -44,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -29,22</t>
+          <t>-71,01; -30,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,42; -29,04</t>
+          <t>-81,98; -27,06</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,09; -5,15</t>
+          <t>-14,22; -5,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -5,77</t>
+          <t>-14,34; -5,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,02; -3,85</t>
+          <t>-11,05; -4,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -3,1</t>
+          <t>-7,96; -2,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-96,55; -63,57</t>
+          <t>-97,0; -64,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-97,81; -67,92</t>
+          <t>-97,78; -64,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-91,9; -48,18</t>
+          <t>-93,22; -52,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-89,62; -60,72</t>
+          <t>-89,69; -57,72</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -12,85</t>
+          <t>-17,6; -13,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,09; -7,45</t>
+          <t>-12,05; -7,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -6,3</t>
+          <t>-10,76; -6,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -1,16</t>
+          <t>-9,66; -1,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,77; -33,23</t>
+          <t>-42,63; -34,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,88; -21,0</t>
+          <t>-32,09; -21,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,76; -18,77</t>
+          <t>-30,1; -18,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,09; -8,97</t>
+          <t>-38,15; -7,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P23_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,05</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-13,33%</t>
+          <t>-16,59%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 3,27</t>
+          <t>-8,49; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 9,01</t>
+          <t>-3,68; 9,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; -1,21</t>
+          <t>-13,53; -1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 6,22</t>
+          <t>-12,49; 5,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 9,9</t>
+          <t>-21,78; 9,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 33,63</t>
+          <t>-10,91; 33,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -3,89</t>
+          <t>-36,57; -3,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 41,81</t>
+          <t>-45,55; 29,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-12,24</t>
+          <t>-9,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-35,27%</t>
+          <t>-28,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -9,27</t>
+          <t>-19,87; -8,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 1,81</t>
+          <t>-9,09; 2,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -0,67</t>
+          <t>-12,23; -0,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -4,83</t>
+          <t>-16,66; -2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,16; -19,68</t>
+          <t>-38,39; -18,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 4,53</t>
+          <t>-19,81; 5,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,99; -1,52</t>
+          <t>-26,17; -0,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,08; -16,46</t>
+          <t>-43,65; -8,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-3,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,27%</t>
+          <t>-13,35%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,58; -9,46</t>
+          <t>-20,67; -9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -6,13</t>
+          <t>-16,85; -6,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -1,11</t>
+          <t>-11,67; -1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,8</t>
+          <t>-8,59; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,93; -19,45</t>
+          <t>-37,52; -19,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,33; -14,03</t>
+          <t>-34,94; -14,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -2,98</t>
+          <t>-27,65; -3,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 7,75</t>
+          <t>-27,95; 4,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>-4,21</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>-15,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -9,45</t>
+          <t>-22,31; -10,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,16; -0,36</t>
+          <t>-12,49; -0,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -1,48</t>
+          <t>-12,87; -1,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 15,12</t>
+          <t>-8,34; -0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,41; -23,53</t>
+          <t>-48,33; -26,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,11; -0,85</t>
+          <t>-25,17; -0,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,46; -3,47</t>
+          <t>-28,15; -4,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 153,65</t>
+          <t>-27,09; -0,21</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,85</t>
+          <t>-8,88</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-28,49%</t>
+          <t>-28,7%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,65; -15,34</t>
+          <t>-27,51; -15,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,59; -14,67</t>
+          <t>-27,01; -15,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -1,96</t>
+          <t>-14,26; -2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,62</t>
+          <t>-13,09; -4,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,35; -51,97</t>
+          <t>-75,82; -52,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,89; -45,22</t>
+          <t>-68,38; -45,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,71; -6,92</t>
+          <t>-41,58; -8,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,38; -15,6</t>
+          <t>-38,84; -15,39</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,57</t>
+          <t>-5,97</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-56,87%</t>
+          <t>-32,46%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -11,88</t>
+          <t>-21,15; -11,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -6,43</t>
+          <t>-16,57; -5,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,69; -4,54</t>
+          <t>-15,19; -4,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,59; -4,9</t>
+          <t>-9,93; -1,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-95,75; -77,03</t>
+          <t>-95,85; -78,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,89; -44,4</t>
+          <t>-82,49; -40,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; -30,84</t>
+          <t>-71,2; -30,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -27,06</t>
+          <t>-46,84; -11,29</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-78,04%</t>
+          <t>-77,59%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -5,32</t>
+          <t>-14,18; -5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; -5,9</t>
+          <t>-14,97; -5,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -4,11</t>
+          <t>-11,22; -3,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; -2,95</t>
+          <t>-8,07; -2,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-97,0; -64,54</t>
+          <t>-96,77; -61,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-97,78; -64,98</t>
+          <t>-98,01; -67,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-93,22; -52,54</t>
+          <t>-92,22; -49,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-89,69; -57,72</t>
+          <t>-90,09; -60,35</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-6,6</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-26,16%</t>
+          <t>-25,82%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -13,2</t>
+          <t>-17,47; -13,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -7,62</t>
+          <t>-12,24; -7,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -6,27</t>
+          <t>-10,92; -6,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -1,31</t>
+          <t>-8,61; -4,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,63; -34,13</t>
+          <t>-42,89; -34,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,09; -21,53</t>
+          <t>-32,26; -21,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,1; -18,97</t>
+          <t>-30,31; -19,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-38,15; -7,79</t>
+          <t>-32,16; -18,44</t>
         </is>
       </c>
     </row>
